--- a/data/trans_orig/P36B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de café o té en 2016</t>
+          <t>Población según la frecuencia de consumo de café o té en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89408</t>
+          <t>88271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125559</t>
+          <t>124151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81827</t>
+          <t>85078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115089</t>
+          <t>117196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181552</t>
+          <t>182752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231183</t>
+          <t>231910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30915</t>
+          <t>30643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>51566</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>6,33%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>36455</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>24830</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>48833</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35994</t>
+          <t>37886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28941</t>
+          <t>27768</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53980</t>
+          <t>51196</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>31478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50160</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>226742</t>
+          <t>227708</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>267805</t>
+          <t>267904</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231060</t>
+          <t>230216</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>269323</t>
+          <t>268782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>469215</t>
+          <t>467728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>522264</t>
+          <t>525485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79749</t>
+          <t>78801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115067</t>
+          <t>113732</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72116</t>
+          <t>74825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106118</t>
+          <t>107841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160986</t>
+          <t>161525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211658</t>
+          <t>208611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18887</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30955</t>
+          <t>31398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23451</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>42295</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41221</t>
+          <t>39030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30133</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55750</t>
+          <t>53997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>420614</t>
+          <t>419837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>460937</t>
+          <t>462298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>411769</t>
+          <t>411138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>451768</t>
+          <t>449889</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>844577</t>
+          <t>845383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>902794</t>
+          <t>902409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65917</t>
+          <t>65086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99517</t>
+          <t>100061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>42273</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70718</t>
+          <t>69955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115802</t>
+          <t>114853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161872</t>
+          <t>159313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>30360</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>23255</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>534170</t>
+          <t>533869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>572101</t>
+          <t>573864</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>561387</t>
+          <t>562132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593411</t>
+          <t>596888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1104174</t>
+          <t>1106023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1156997</t>
+          <t>1156570</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72191</t>
+          <t>69498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33901</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61191</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82205</t>
+          <t>81561</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119331</t>
+          <t>119523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>18115</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13626</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14936</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>26826</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>10336</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>26997</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>549192</t>
+          <t>551358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>584252</t>
+          <t>585748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>557528</t>
+          <t>558881</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>590284</t>
+          <t>591591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1122534</t>
+          <t>1122791</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1166872</t>
+          <t>1167094</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37958</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67785</t>
+          <t>65822</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34318</t>
+          <t>33268</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62757</t>
+          <t>60930</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>77645</t>
+          <t>78095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>118224</t>
+          <t>117643</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22762</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11934</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31232</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>382759</t>
+          <t>384070</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>416481</t>
+          <t>417495</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>415546</t>
+          <t>418425</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>448797</t>
+          <t>449062</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>811627</t>
+          <t>812146</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>858300</t>
+          <t>858463</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>31623</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>54425</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>33671</t>
+          <t>33597</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>59230</t>
+          <t>59602</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>73225</t>
+          <t>73073</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>106989</t>
+          <t>106308</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>263905</t>
+          <t>261963</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>289961</t>
+          <t>288494</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>305858</t>
+          <t>305594</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>333458</t>
+          <t>334012</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>578199</t>
+          <t>579046</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>615006</t>
+          <t>616092</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>34102</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>54406</t>
+          <t>54635</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>56822</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>92003</t>
+          <t>94730</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>96903</t>
+          <t>97669</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>139077</t>
+          <t>138975</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,47 +5083,47 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>12552</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>4557</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
           <t>1210</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>12772</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>14639</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>194428</t>
+          <t>195392</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>216698</t>
+          <t>217783</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>293612</t>
+          <t>293103</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>330675</t>
+          <t>331053</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>495875</t>
+          <t>497544</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>540196</t>
+          <t>541403</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>436947</t>
+          <t>436231</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>516099</t>
+          <t>520007</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,47 +5519,47 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>455464</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>417344</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>499845</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
           <t>12,89%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>15,22%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>455464</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>413553</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>497229</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>878328</t>
+          <t>878727</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>988830</t>
+          <t>988479</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>50200</t>
+          <t>50948</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>83656</t>
+          <t>83617</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>34929</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>62522</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>94409</t>
+          <t>95601</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>134890</t>
+          <t>136455</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>55175</t>
+          <t>54547</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>88277</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>69983</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>152741</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>66102</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>101943</t>
+          <t>103138</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>57210</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>92000</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>130312</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>182036</t>
+          <t>177579</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2648102</t>
+          <t>2649657</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2743943</t>
+          <t>2743991</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2854982</t>
+          <t>2855265</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2949996</t>
+          <t>2949108</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5538480</t>
+          <t>5528900</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5667884</t>
+          <t>5665908</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88271</t>
+          <t>88759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124151</t>
+          <t>123910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85078</t>
+          <t>82379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117196</t>
+          <t>116092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>182752</t>
+          <t>181503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231910</t>
+          <t>229468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30643</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51566</t>
+          <t>50968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>21850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>27882</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>51544</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>29133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>26388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50431</t>
+          <t>51001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227708</t>
+          <t>228292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>267904</t>
+          <t>267972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230216</t>
+          <t>229575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>268782</t>
+          <t>267293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>467728</t>
+          <t>469231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>525485</t>
+          <t>521697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78801</t>
+          <t>79822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113732</t>
+          <t>113642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74825</t>
+          <t>73074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>104815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161525</t>
+          <t>161575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208611</t>
+          <t>209722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18887</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31398</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>23367</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>25216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42295</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39030</t>
+          <t>39935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>21013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28949</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53997</t>
+          <t>54401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>419837</t>
+          <t>419821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>462298</t>
+          <t>460467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>411138</t>
+          <t>413426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>449889</t>
+          <t>450250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>845383</t>
+          <t>844557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>902409</t>
+          <t>903204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65086</t>
+          <t>65513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100061</t>
+          <t>99867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42273</t>
+          <t>43141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69955</t>
+          <t>71230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114853</t>
+          <t>117633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159313</t>
+          <t>162145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,82 +2222,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10387</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>11439</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>5764</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>20745</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4123</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1049</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>10213</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>11439</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>5148</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>20348</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25700</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30360</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23255</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16084</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>36570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>533869</t>
+          <t>533357</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>573864</t>
+          <t>572956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>562132</t>
+          <t>559548</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>596888</t>
+          <t>592916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1106023</t>
+          <t>1103175</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1156570</t>
+          <t>1156354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>40013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69498</t>
+          <t>68698</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60829</t>
+          <t>60157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81561</t>
+          <t>80767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119523</t>
+          <t>123725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26826</t>
+          <t>27198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>551358</t>
+          <t>552349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>585748</t>
+          <t>585450</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>558881</t>
+          <t>560291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>591591</t>
+          <t>592363</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1122791</t>
+          <t>1121081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1167094</t>
+          <t>1171168</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37716</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65822</t>
+          <t>68097</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>33491</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60930</t>
+          <t>62176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78095</t>
+          <t>79420</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>117643</t>
+          <t>119327</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>30911</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>384070</t>
+          <t>383503</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>417495</t>
+          <t>418626</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>418425</t>
+          <t>415947</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>449062</t>
+          <t>448671</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>812146</t>
+          <t>810168</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>858463</t>
+          <t>857153</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31623</t>
+          <t>32388</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>56728</t>
+          <t>55099</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>59602</t>
+          <t>60033</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>73073</t>
+          <t>72053</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>106308</t>
+          <t>106089</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>261963</t>
+          <t>262921</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>288494</t>
+          <t>289619</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>305594</t>
+          <t>306412</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>334012</t>
+          <t>333148</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>579046</t>
+          <t>578908</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>616092</t>
+          <t>616167</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>33247</t>
+          <t>33227</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>54635</t>
+          <t>55504</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>94730</t>
+          <t>91366</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>97669</t>
+          <t>98286</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>138975</t>
+          <t>137525</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>15228</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>195392</t>
+          <t>193654</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>217783</t>
+          <t>217436</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>293103</t>
+          <t>293710</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>331053</t>
+          <t>332723</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>497544</t>
+          <t>495848</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>541403</t>
+          <t>539879</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>436231</t>
+          <t>434989</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>520007</t>
+          <t>517337</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>417344</t>
+          <t>416658</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>499845</t>
+          <t>496841</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>878727</t>
+          <t>877144</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>988479</t>
+          <t>987209</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>50948</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>83041</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>63745</t>
+          <t>64020</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>95601</t>
+          <t>94413</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>136455</t>
+          <t>138050</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>54547</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>88277</t>
+          <t>88562</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>40461</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>68907</t>
+          <t>69748</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>103528</t>
+          <t>103727</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>152741</t>
+          <t>149661</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>66102</t>
+          <t>66774</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>103138</t>
+          <t>104304</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>55699</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>90525</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>131257</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>177579</t>
+          <t>181261</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2649657</t>
+          <t>2652089</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2743991</t>
+          <t>2747420</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2855265</t>
+          <t>2851640</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2949108</t>
+          <t>2951726</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5528900</t>
+          <t>5538958</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5665908</t>
+          <t>5670506</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
